--- a/Assets/Data/Dungeon0064.xlsx
+++ b/Assets/Data/Dungeon0064.xlsx
@@ -59,10 +59,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -80,8 +80,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -103,45 +104,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -155,9 +132,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,7 +155,30 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -186,28 +192,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -217,10 +201,26 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -233,25 +233,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,7 +251,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,7 +281,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,25 +329,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,61 +341,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,13 +365,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,13 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,6 +424,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -442,17 +481,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -482,48 +524,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -532,145 +532,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0064.xlsx
+++ b/Assets/Data/Dungeon0064.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -42,6 +42,9 @@
     <t>InitDir</t>
   </si>
   <si>
+    <t>□</t>
+  </si>
+  <si>
     <t>■</t>
   </si>
   <si>
@@ -61,8 +64,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -80,11 +83,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -103,75 +121,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,23 +138,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,7 +176,52 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,37 +236,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,31 +254,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,19 +272,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,7 +296,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,13 +338,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,25 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,6 +427,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -451,6 +465,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -462,30 +485,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,13 +513,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -532,7 +535,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -541,7 +544,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -550,127 +553,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1483,13 +1486,13 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -1554,28 +1557,28 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>8</v>
@@ -1625,20 +1628,20 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>8</v>
@@ -1688,28 +1691,28 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>8</v>
@@ -1759,13 +1762,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -3292,43 +3295,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -3363,43 +3366,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -3434,43 +3437,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -3505,43 +3508,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -3576,43 +3579,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -3647,43 +3650,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -3718,35 +3721,35 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -3781,43 +3784,43 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -3852,43 +3855,43 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -3919,43 +3922,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -3986,43 +3989,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -4056,43 +4059,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -4124,43 +4127,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
